--- a/EMC/EMC-Calculations.xlsx
+++ b/EMC/EMC-Calculations.xlsx
@@ -5,17 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LTspice\Simulation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LTspice\Simulation\EMC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643703D5-A2A7-4ADB-B981-F9347443352A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE6A8A1-1DB7-40E9-821B-AD9177E2FACA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Limits" sheetId="1" r:id="rId1"/>
-    <sheet name="Calculation" sheetId="2" r:id="rId2"/>
-    <sheet name="Harmonics" sheetId="4" r:id="rId3"/>
+    <sheet name="Cx-Cy-CMC Calculation" sheetId="2" r:id="rId2"/>
+    <sheet name="Y-Cap Leakage Currents" sheetId="5" r:id="rId3"/>
+    <sheet name="Caps Discharge Resistor" sheetId="6" r:id="rId4"/>
+    <sheet name="VARISTOR" sheetId="7" r:id="rId5"/>
+    <sheet name="Harmonics" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="102">
   <si>
     <t>In a typical power system, the noise profile looks like this:</t>
   </si>
@@ -86,15 +89,6 @@
     <t>Radiated disturbance (30MHz to 1000MHz)</t>
   </si>
   <si>
-    <t>1. „LC“ = 44dB/Dec</t>
-  </si>
-  <si>
-    <t>Desired damping CM&amp;DM = 44dB @ fsw(100kHz)</t>
-  </si>
-  <si>
-    <t>2. Filter corner frequency</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -177,7 +171,303 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">3. Define </t>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YT =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CM =</t>
+    </r>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>mH</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CM =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FSW-CM =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dm =</t>
+    </r>
+  </si>
+  <si>
+    <t>Common Mode Choke leakage Inductance</t>
+  </si>
+  <si>
+    <t>nF</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>µ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+  </si>
+  <si>
+    <t>µH</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CY1 = 10nF - CY2  = 10nF</t>
+  </si>
+  <si>
+    <t>LCM = 36mH chosen</t>
+  </si>
+  <si>
+    <r>
+      <t>CX = 2.2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>µ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H chosen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dm =</t>
+    </r>
+  </si>
+  <si>
+    <t>Summary Checklist for Harmonics</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Modification</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Bridge Rectifier</t>
+  </si>
+  <si>
+    <t>Use "Fast" or "Soft" recovery diodes</t>
+  </si>
+  <si>
+    <t>Reduces high-order switching harmonics</t>
+  </si>
+  <si>
+    <t>Inductors</t>
+  </si>
+  <si>
+    <t>Increase DM Inductance</t>
+  </si>
+  <si>
+    <t>Widens conduction angle; lowers $THD$</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>Decrease Bulk Capacitance</t>
+  </si>
+  <si>
+    <t>Reduces peak current magnitude</t>
+  </si>
+  <si>
+    <t>Circuitry</t>
+  </si>
+  <si>
+    <t>Add Active PFC</t>
+  </si>
+  <si>
+    <t>Gold standard for passing IEC 61000-3-2</t>
+  </si>
+  <si>
+    <t>1. We will use 1-stage LC Filter to achieve desired damping CM&amp;DM @ Fsw</t>
+  </si>
+  <si>
+    <t>Desired damping CM&amp;DM @ Fsw</t>
+  </si>
+  <si>
+    <t>2. Calculate Filter corner frequency for the filter</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. Calculate </t>
     </r>
     <r>
       <rPr>
@@ -188,6 +478,41 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_cm for the calculate Fc</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Recalculate the a𝑐𝑡𝑢𝑎𝑙 F𝑐𝑚 with the chosen values</t>
+  </si>
+  <si>
+    <t>6. Recalculate the a𝑐𝑡𝑢𝑎𝑙  Afsw-cm with the chosen values</t>
+  </si>
+  <si>
+    <t>7.Choose Cx value</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Choose </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Y</t>
     </r>
     <r>
@@ -198,7 +523,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">-caps --&gt; 10nF x 2 --&gt; 20nF total </t>
+      <t xml:space="preserve">-caps values --&gt; 10nF x 2 --&gt; 20nF total </t>
     </r>
     <r>
       <rPr>
@@ -223,40 +548,68 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">4. Define </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L</t>
-    </r>
+    <t>8.  Recalculate the a𝑐𝑡𝑢𝑎𝑙 F𝑑𝑚 with the chosen values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Recalculate the a𝑐𝑡𝑢𝑎𝑙 A𝑑𝑚 with the chosen values </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X1 =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X2 =</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">_cm for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>f</t>
+      </rPr>
+      <t>n</t>
     </r>
     <r>
       <rPr>
@@ -266,7 +619,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>c = 7.94kHz</t>
+      <t>F</t>
     </r>
   </si>
   <si>
@@ -279,6 +632,84 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mains =</t>
+    </r>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mains =</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst Case Tolerance: Grid Voltage +10%; Capacitance +20% </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mains +10% =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>C</t>
     </r>
     <r>
@@ -290,7 +721,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>YT =</t>
+      <t>X1 +20% =</t>
     </r>
   </si>
   <si>
@@ -303,7 +734,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>L</t>
+      <t>C</t>
     </r>
     <r>
       <rPr>
@@ -314,17 +745,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>CM =</t>
-    </r>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>mH</t>
-  </si>
-  <si>
-    <t>5. 𝐴𝑐𝑡𝑢𝑎𝑙 𝑓𝑐𝑚</t>
+      <t>X2 +20% =</t>
+    </r>
   </si>
   <si>
     <r>
@@ -336,7 +758,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>F</t>
+      <t>I</t>
     </r>
     <r>
       <rPr>
@@ -347,33 +769,231 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>CM =</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">6. Actual </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
+      <t>leakge =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YL =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YN =</t>
+    </r>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>mA</t>
+  </si>
+  <si>
+    <t>Max Standard Value is 50nF to match the max allowable leakage current = 3.5 mA</t>
+  </si>
+  <si>
+    <t>Max allowable leakage current = 3.5 mA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>paraMOV =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tot =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mains*sqrt(2) =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tot+20% =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discharge &lt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Ω</t>
+  </si>
+  <si>
+    <t>KΩ</t>
+  </si>
+  <si>
+    <t>Chosen 220 kΩ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discharge +10%</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>fsw-cm</t>
+      <t xml:space="preserve"> =</t>
     </r>
   </si>
   <si>
@@ -386,7 +1006,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A</t>
+      <t>P</t>
     </r>
     <r>
       <rPr>
@@ -397,11 +1017,28 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>FSW-CM =</t>
-    </r>
-  </si>
-  <si>
-    <t>7. Define Cx</t>
+      <t>Rating</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =</t>
+    </r>
+  </si>
+  <si>
+    <t>Watt</t>
+  </si>
+  <si>
+    <t>mWatt</t>
+  </si>
+  <si>
+    <t>1. Operating voltage:</t>
   </si>
   <si>
     <r>
@@ -413,7 +1050,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>C</t>
+      <t>U</t>
     </r>
     <r>
       <rPr>
@@ -424,7 +1061,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>X =</t>
+      <t>Q,eff =</t>
     </r>
   </si>
   <si>
@@ -437,7 +1074,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>L</t>
+      <t>V</t>
     </r>
     <r>
       <rPr>
@@ -448,151 +1085,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>dm =</t>
-    </r>
-  </si>
-  <si>
-    <t>Common Mode Choke leakage Inductance</t>
-  </si>
-  <si>
-    <t>nF</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>µ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-  </si>
-  <si>
-    <t>µH</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CY1 = 10nF - CY2  = 10nF</t>
-  </si>
-  <si>
-    <t>LCM = 36mH chosen</t>
-  </si>
-  <si>
-    <r>
-      <t>CX = 2.2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>µ</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H chosen</t>
-    </r>
-  </si>
-  <si>
-    <t>8. 𝐴𝑐𝑡𝑢𝑎𝑙 𝑓𝑑𝑚</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>dm =</t>
-    </r>
-  </si>
-  <si>
-    <t>9. 𝐴𝑐𝑡𝑢𝑎𝑙 A𝑑𝑚</t>
-  </si>
-  <si>
-    <t>Summary Checklist for Harmonics</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Modification</t>
-  </si>
-  <si>
-    <t>Effect</t>
-  </si>
-  <si>
-    <t>Bridge Rectifier</t>
-  </si>
-  <si>
-    <t>Use "Fast" or "Soft" recovery diodes</t>
-  </si>
-  <si>
-    <t>Reduces high-order switching harmonics</t>
-  </si>
-  <si>
-    <t>Inductors</t>
-  </si>
-  <si>
-    <t>Increase DM Inductance</t>
-  </si>
-  <si>
-    <t>Widens conduction angle; lowers $THD$</t>
-  </si>
-  <si>
-    <t>Capacitor</t>
-  </si>
-  <si>
-    <t>Decrease Bulk Capacitance</t>
-  </si>
-  <si>
-    <t>Reduces peak current magnitude</t>
-  </si>
-  <si>
-    <t>Circuitry</t>
-  </si>
-  <si>
-    <t>Add Active PFC</t>
-  </si>
-  <si>
-    <t>Gold standard for passing IEC 61000-3-2</t>
+      <t>Operating for Varistor =</t>
+    </r>
+  </si>
+  <si>
+    <t>For AC:-</t>
+  </si>
+  <si>
+    <t>For DC:-</t>
   </si>
 </sst>
 </file>
@@ -720,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -749,11 +1249,97 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -771,14 +1357,106 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>537457</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>131750</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>82963</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4319AFE6-40DA-4121-AF38-7ACC117C2405}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="847" t="1321"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1147057" y="2339340"/>
+          <a:ext cx="6848533" cy="3656743"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>651</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>56271</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A589065A-A764-496C-B173-67EA24543E99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1143000" y="6096651"/>
+          <a:ext cx="6804660" cy="3713220"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>271525</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>140539</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>750139</xdr:colOff>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>28267</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -816,13 +1494,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>148204</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>384622</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>112325</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -860,13 +1538,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>8468</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>476057</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>70404</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -904,13 +1582,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>405344</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>108435</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>718035</xdr:colOff>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -947,13 +1625,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>704662</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>118041</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -991,13 +1669,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>167640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>757992</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>180905</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1035,13 +1713,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>161736</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>429986</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>96084</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1067,6 +1745,285 @@
         <a:xfrm>
           <a:off x="1234440" y="16803816"/>
           <a:ext cx="2007326" cy="665868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>18918</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1870992</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>176325</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB59AD67-C2B2-4155-8F70-036434DB8B50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="624840" y="201798"/>
+          <a:ext cx="5254272" cy="2717727"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>133656</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>787958</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>161748</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{147D6204-C3FD-4371-9330-3DE1D58447D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1013460" y="7288836"/>
+          <a:ext cx="3782618" cy="942492"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>512795</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>98312</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C4B7D9B-E250-4DC3-BFAA-0FE8635E5293}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647700" y="207292"/>
+          <a:ext cx="8140415" cy="3914380"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>30313</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>58566</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>97013</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEA0A97D-9AAB-414B-ACE5-BB9A5C4A0289}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1287780" y="8648533"/>
+          <a:ext cx="3388506" cy="981100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>101890</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>399467</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>22760</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2450527-E47A-4FBD-B2B4-F597D17C6953}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1211580" y="10693690"/>
+          <a:ext cx="3805607" cy="652390"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>594361</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>121608</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>174593</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DD6CF39-8A95-4A94-B5FB-632F281348F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594361" y="487368"/>
+          <a:ext cx="6675120" cy="2613305"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1428,256 +2385,671 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0758AB7F-84D8-4B6F-878D-F1FAE6661672}">
-  <dimension ref="B2:F86"/>
+  <dimension ref="B1:J83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="1" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="5">
+        <v>100</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+    <row r="18" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C18" s="4" t="s">
         <v>21</v>
+      </c>
+      <c r="D18" s="5">
+        <v>44</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="6">
+        <f>(D16*10^3)/(10^(D18/40))</f>
+        <v>7943.2823472428099</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="6">
+        <f>D20/1000</f>
+        <v>7.9432823472428096</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F25" s="15"/>
+    </row>
+    <row r="26" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="5">
+        <v>20</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="6">
+        <f>1/(((2*PI()*D20)^2)*(D32*10^-9))</f>
+        <v>2.0072906775855458E-2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D35" s="6">
+        <f>D34*1000</f>
+        <v>20.072906775855458</v>
+      </c>
+      <c r="E35" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C44" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="6">
+        <f>1/(2*PI()*SQRT(36*10^-3*20*10^-9))</f>
+        <v>5931.354528476475</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C45" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="6">
+        <f>D44/1000</f>
+        <v>5.9313545284764748</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B48" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C55" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="6">
+        <f>LOG(D16/D45)*40</f>
+        <v>49.07384466294998</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5" t="str">
+        <f>IF(OR(D55&gt;D18, D55=D18),"Attenuation Achieved ","Attenuation not Achieved, Recalculate Again")</f>
+        <v xml:space="preserve">Attenuation Achieved </v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C62" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="5">
+        <v>200</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C64" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" s="5">
+        <f>1/(((2*PI()*D20)^2)*(D62*10^-6))</f>
+        <v>2.007290677585546E-6</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D65" s="6">
+        <f>D64*10^6</f>
+        <v>2.0072906775855461</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C74" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D74" s="5">
+        <f>1/(2*PI()*SQRT(200*10^-6*2.2*10^-6))</f>
+        <v>7587.4142065816714</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C75" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" s="6">
+        <f>D74/1000</f>
+        <v>7.5874142065816716</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="83" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C83" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" s="6">
+        <f>LOG(D16/D75)*40</f>
+        <v>44.796248264048344</v>
+      </c>
+      <c r="F83" s="5" t="str">
+        <f>IF(OR(D83&gt;D18, D83=D18),"Attenuation Achieved ","Attenuation not Achieved, Recalculate Again")</f>
+        <v xml:space="preserve">Attenuation Achieved </v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F24:J24"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F83">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Attenuation not Achieved, Recalculate Again">
+      <formula>NOT(ISERROR(SEARCH("Attenuation not Achieved, Recalculate Again",F83)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Attenuation Achieved">
+      <formula>NOT(ISERROR(SEARCH("Attenuation Achieved",F83)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F55">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Attenuation not Achieved, Recalculate Again">
+      <formula>NOT(ISERROR(SEARCH("Attenuation not Achieved, Recalculate Again",F55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Attenuation Achieved">
+      <formula>NOT(ISERROR(SEARCH("Attenuation Achieved",F55)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A279A00B-C7FB-49B4-9128-D87A076CD280}">
+  <dimension ref="B18:H42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" customWidth="1"/>
+    <col min="8" max="8" width="34.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="18" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C19" s="4" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D19" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C21" s="4" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="D21" s="5">
-        <v>44</v>
+        <v>5.6</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="C23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="6">
-        <f>(D19*10^3)/(10^(D21/40))</f>
-        <v>7943.2823472428099</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>27</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="6">
-        <f>D23/1000</f>
-        <v>7.9432823472428096</v>
+        <v>71</v>
+      </c>
+      <c r="D24" s="5">
+        <v>230</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="5">
+        <v>50</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C30" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="5">
+        <f>1.1*D24</f>
+        <v>253.00000000000003</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="5">
+        <f>1.2*D18</f>
+        <v>1.2</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="5">
+        <f>1.2*D19</f>
+        <v>1.2</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C40" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="5">
+        <f>D30*2*PI()*D26*((D21*10^-9)+((((D31+D32)*10^-6)*(D22*10^-9))/(((D31+D32)*10^-6)+(D22*10^-9))))</f>
+        <v>8.8916554336339738E-4</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="6">
+        <f>D40*1000</f>
+        <v>0.88916554336339737</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" s="5"/>
+      <c r="G41" s="14" t="str">
+        <f>IF(D41&lt;3.5,"Will Pass Leakage Current Test","Will not Pass Leakage Current Test, Please choose lower Cy Value")</f>
+        <v>Will Pass Leakage Current Test</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G42" s="15"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G41">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Will not Pass Leakage Current Test, Please choose lower Cy Value">
+      <formula>NOT(ISERROR(SEARCH("Will not Pass Leakage Current Test, Please choose lower Cy Value",G41)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Will Pass Leakage Current Test">
+      <formula>NOT(ISERROR(SEARCH("Will Pass Leakage Current Test",G41)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4489072B-AE50-47DD-8DAD-B5CBE02126D9}">
+  <dimension ref="C25:F63"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="25" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C28" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C29" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="5">
+        <v>100</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C33" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="6">
+        <f>230*SQRT(2)</f>
+        <v>325.26911934581187</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C35" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="5">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="D35" s="6">
+        <f>1.1*D33</f>
+        <v>357.79603128039309</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C37" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D37">
-        <f>1/(((2*PI()*D23)^2)*(D35*10^-9))</f>
-        <v>2.0072906775855458E-2</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38">
-        <f>D37*1000</f>
-        <v>20.072906775855458</v>
-      </c>
-      <c r="E38" t="s">
-        <v>33</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="D37" s="5">
+        <f>(D25*10^-6)+(D26*10^-6)+(D31*10^-9)+(1/((1/(D28*10^-9))+(1/(D29*10^-9))))</f>
+        <v>2.1028E-6</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="D38" s="13">
+        <f>D37*10^6</f>
+        <v>2.1028000000000002</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C39" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" s="6">
+        <f>1.2*D38</f>
+        <v>2.5233600000000003</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C47" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D47" s="5">
-        <f>1/(2*PI()*SQRT(36*10^-3*20*10^-9))</f>
-        <v>5931.354528476475</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="C48" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D48" s="6">
+        <v>89</v>
+      </c>
+      <c r="D47" s="6">
+        <f>(((-LN(60/D35))/1)^-1)/(D39*10^-6)</f>
+        <v>221938.22314171676</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="D48">
         <f>D47/1000</f>
-        <v>5.9313545284764748</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B51" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+        <v>221.93822314171678</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C56" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="17">
+        <v>230</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C58" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D58" s="5">
-        <f>LOG(D19/D48)*40</f>
-        <v>49.07384466294998</v>
-      </c>
-      <c r="E58" s="5"/>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B60" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="C65" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D65" s="5">
-        <v>200</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="C67" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D67" s="5">
-        <f>1/(((2*PI()*D23)^2)*(D65*10^-6))</f>
-        <v>2.007290677585546E-6</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D68" s="5">
-        <f>D67*10^6</f>
-        <v>2.0072906775855461</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="C77" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D77" s="5">
-        <f>1/(2*PI()*SQRT(200*10^-6*2.2*10^-6))</f>
-        <v>7587.4142065816714</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="C78" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D78" s="6">
-        <f>D77/1000</f>
-        <v>7.5874142065816716</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="86" spans="3:4" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="C86" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D86" s="5">
-        <f>LOG(D19/D78)*40</f>
-        <v>44.796248264048344</v>
+        <v>75</v>
+      </c>
+      <c r="D58" s="17">
+        <f>1.1*D56</f>
+        <v>253.00000000000003</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C60" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="5">
+        <f>1.1*220</f>
+        <v>242.00000000000003</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C62" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" s="5">
+        <f>(D58)^2/(D60*10^3)</f>
+        <v>0.26450000000000001</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C63" s="10"/>
+      <c r="D63" s="10">
+        <f>D62*1000</f>
+        <v>264.5</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1686,7 +3058,107 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D52C64B9-E795-47AC-8A1E-29319F235A34}">
+  <dimension ref="B2:E30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="17">
+        <v>230</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="6">
+        <f>D19*1.21</f>
+        <v>278.3</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C23" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="17">
+        <f>D21*1.078</f>
+        <v>300.00740000000002</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B25" s="18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C26" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="17">
+        <v>24</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C28" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="6">
+        <f>D26*1.21</f>
+        <v>29.04</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="C30" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="17">
+        <f>D28*1.078</f>
+        <v>31.305120000000002</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A82038F-61F4-453F-9D67-43682C57C34C}">
   <dimension ref="B3:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1698,63 +3170,63 @@
   <sheetData>
     <row r="3" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="2:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/EMC/EMC-Calculations.xlsx
+++ b/EMC/EMC-Calculations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LTspice\Simulation\EMC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE6A8A1-1DB7-40E9-821B-AD9177E2FACA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941578A1-2F93-4A75-BE2F-00D378628660}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Limits" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="123">
   <si>
     <t>In a typical power system, the noise profile looks like this:</t>
   </si>
@@ -320,9 +320,6 @@
     </r>
   </si>
   <si>
-    <t>Common Mode Choke leakage Inductance</t>
-  </si>
-  <si>
     <t>nF</t>
   </si>
   <si>
@@ -959,9 +956,6 @@
     <t>KΩ</t>
   </si>
   <si>
-    <t>Chosen 220 kΩ</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1093,13 +1087,82 @@
   </si>
   <si>
     <t>For DC:-</t>
+  </si>
+  <si>
+    <t>For home appliances is 0.75mA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common Mode is Good </t>
+  </si>
+  <si>
+    <t>Common Mode choke is good</t>
+  </si>
+  <si>
+    <t>Y-Caps are Good</t>
+  </si>
+  <si>
+    <t>Earth Length and addressing are Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problem is in differential mode </t>
+  </si>
+  <si>
+    <t xml:space="preserve">X-caps need to increase </t>
+  </si>
+  <si>
+    <t>Leakage inductane of common mode need to increae</t>
+  </si>
+  <si>
+    <t>Adding DM inductore in L or N or both.</t>
+  </si>
+  <si>
+    <t>1-</t>
+  </si>
+  <si>
+    <t>2-</t>
+  </si>
+  <si>
+    <t>3-</t>
+  </si>
+  <si>
+    <t>4-</t>
+  </si>
+  <si>
+    <t>Control Ports</t>
+  </si>
+  <si>
+    <t>AC L,N Ports</t>
+  </si>
+  <si>
+    <t>Ferrite  cores are good for DV</t>
+  </si>
+  <si>
+    <t>Common Mode has two peaks</t>
+  </si>
+  <si>
+    <t>Ferrite  cores need to make more turns</t>
+  </si>
+  <si>
+    <t>Y-Caps need to increase</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>Common Mode Choke leakage Inductance approximately 1% from Inductance value</t>
+  </si>
+  <si>
+    <t>Chosen 1 MΩ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1172,8 +1235,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1189,6 +1268,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1220,7 +1311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1267,13 +1358,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1357,22 +1460,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>537457</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:colOff>323851</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>109179</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>131750</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>82963</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>167641</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>159253</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4319AFE6-40DA-4121-AF38-7ACC117C2405}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F99768C7-407D-4E41-8A01-090A46F7A0D6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1380,15 +1483,16 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect l="847" t="1321"/>
-        <a:stretch/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1147057" y="2339340"/>
-          <a:ext cx="6848533" cy="3656743"/>
+          <a:off x="933451" y="2364699"/>
+          <a:ext cx="6488430" cy="3707674"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1400,22 +1504,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>651</xdr:rowOff>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>133398</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>56271</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>138288</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A589065A-A764-496C-B173-67EA24543E99}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB8642F-41ED-4946-8D85-E2435BF8DE92}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1431,8 +1535,228 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1143000" y="6096651"/>
-          <a:ext cx="6804660" cy="3713220"/>
+          <a:off x="944880" y="6229398"/>
+          <a:ext cx="6522720" cy="4028250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>153641</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>138369</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCD80B68-547E-4703-AFDC-D55AEEEEB8AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="906780" y="11187401"/>
+          <a:ext cx="6629400" cy="4008088"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>263377</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>149834</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9416C5E2-DA4E-43D7-93D3-568B91813C51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="872977" y="20147280"/>
+          <a:ext cx="6625103" cy="4020794"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>267310</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>144779</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>168891</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D19ED941-2479-4A5A-B38A-E9ADEF016661}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876910" y="16367760"/>
+          <a:ext cx="6522109" cy="3430251"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>328520</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>126512</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>4988</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{389664CE-390B-41FB-B773-9AA493434053}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="938120" y="25488900"/>
+          <a:ext cx="7052232" cy="4569368"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>323040</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>117427</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42F6C4BA-A0AB-4539-831A-D8C927BA4BFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="932640" y="30342840"/>
+          <a:ext cx="6999780" cy="4034107"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2298,36 +2622,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:E12"/>
+  <dimension ref="A3:H138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="28.21875" customWidth="1"/>
     <col min="4" max="4" width="27.6640625" customWidth="1"/>
     <col min="5" max="5" width="32.109375" customWidth="1"/>
+    <col min="7" max="7" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="3:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
@@ -2338,7 +2664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
@@ -2349,7 +2675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
@@ -2360,7 +2686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2371,7 +2697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C12" s="2" t="s">
         <v>13</v>
       </c>
@@ -2382,7 +2708,227 @@
         <v>15</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C18" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+    </row>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G27" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G28" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G29" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G30" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G33" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H33" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G34" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G35" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H35" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G36" s="19"/>
+    </row>
+    <row r="66" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C66" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+    </row>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+    </row>
+    <row r="73" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="74" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G74" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H74" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="75" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G75" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H75" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G76" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H76" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G77" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H77" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="79" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G79" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G80" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H80" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G81" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H81" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="82" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G82" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H82" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B137" s="22"/>
+      <c r="C137" s="22"/>
+      <c r="D137" s="22"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="22"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="22"/>
+      <c r="B138" s="22"/>
+      <c r="C138" s="22"/>
+      <c r="D138" s="22"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C66:E67"/>
+    <mergeCell ref="C18:E19"/>
+    <mergeCell ref="A15:G16"/>
+    <mergeCell ref="A137:G138"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -2402,12 +2948,12 @@
   <sheetData>
     <row r="1" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="2:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
@@ -2426,13 +2972,13 @@
         <v>21</v>
       </c>
       <c r="D18" s="5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
@@ -2441,7 +2987,7 @@
       </c>
       <c r="D20" s="6">
         <f>(D16*10^3)/(10^(D18/40))</f>
-        <v>7943.2823472428099</v>
+        <v>10000</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>24</v>
@@ -2453,7 +2999,7 @@
       </c>
       <c r="D21" s="6">
         <f>D20/1000</f>
-        <v>7.9432823472428096</v>
+        <v>10</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>20</v>
@@ -2461,22 +3007,22 @@
     </row>
     <row r="24" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
+        <v>64</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F25" s="15"/>
     </row>
     <row r="26" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
@@ -2487,10 +3033,10 @@
         <v>20</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
@@ -2499,7 +3045,7 @@
       </c>
       <c r="D34" s="6">
         <f>1/(((2*PI()*D20)^2)*(D32*10^-9))</f>
-        <v>2.0072906775855458E-2</v>
+        <v>1.2665147955292222E-2</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2508,18 +3054,18 @@
     <row r="35" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D35" s="6">
         <f>D34*1000</f>
-        <v>20.072906775855458</v>
+        <v>12.665147955292221</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
@@ -2546,12 +3092,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C55" s="4" t="s">
         <v>30</v>
       </c>
@@ -2565,61 +3111,65 @@
         <v xml:space="preserve">Attenuation Achieved </v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C62" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D62" s="5">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+    </row>
+    <row r="64" spans="2:10" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C64" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D64" s="5">
         <f>1/(((2*PI()*D20)^2)*(D62*10^-6))</f>
-        <v>2.007290677585546E-6</v>
+        <v>7.0361933084956796E-7</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D65" s="6">
         <f>D64*10^6</f>
-        <v>2.0072906775855461</v>
+        <v>0.70361933084956796</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C74" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D74" s="5">
-        <f>1/(2*PI()*SQRT(200*10^-6*2.2*10^-6))</f>
-        <v>7587.4142065816714</v>
+        <f>1/(2*PI()*SQRT(360*10^-6*2.2*10^-6))</f>
+        <v>5655.3246464547501</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>24</v>
@@ -2627,11 +3177,11 @@
     </row>
     <row r="75" spans="2:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C75" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D75" s="6">
         <f>D74/1000</f>
-        <v>7.5874142065816716</v>
+        <v>5.6553246464547504</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>20</v>
@@ -2639,7 +3189,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
@@ -2648,7 +3198,7 @@
       </c>
       <c r="D83" s="6">
         <f>LOG(D16/D75)*40</f>
-        <v>44.796248264048344</v>
+        <v>49.901698366114466</v>
       </c>
       <c r="F83" s="5" t="str">
         <f>IF(OR(D83&gt;D18, D83=D18),"Attenuation Achieved ","Attenuation not Achieved, Recalculate Again")</f>
@@ -2656,8 +3206,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="F24:J24"/>
+    <mergeCell ref="F62:J62"/>
   </mergeCells>
   <conditionalFormatting sqref="F83">
     <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Attenuation not Achieved, Recalculate Again">
@@ -2683,7 +3234,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A279A00B-C7FB-49B4-9128-D87A076CD280}">
-  <dimension ref="B18:H42"/>
+  <dimension ref="B18:H43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
@@ -2693,62 +3244,62 @@
   <sheetData>
     <row r="18" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C18" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" s="5">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C19" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D19" s="5">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C21" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" s="5">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C22" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" s="5">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C24" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D24" s="5">
         <v>230</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C26" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26" s="5">
         <v>50</v>
@@ -2759,64 +3310,64 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C30" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="5">
         <f>1.1*D24</f>
         <v>253.00000000000003</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C31" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" s="5">
         <f>1.2*D18</f>
-        <v>1.2</v>
+        <v>2.64</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D32" s="5">
         <f>1.2*D19</f>
-        <v>1.2</v>
+        <v>2.64</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="3:8" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C40" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D40" s="5">
         <f>D30*2*PI()*D26*((D21*10^-9)+((((D31+D32)*10^-6)*(D22*10^-9))/(((D31+D32)*10^-6)+(D22*10^-9))))</f>
-        <v>8.8916554336339738E-4</v>
+        <v>1.5881433818821101E-3</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="3:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D41" s="6">
         <f>D40*1000</f>
-        <v>0.88916554336339737</v>
+        <v>1.58814338188211</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="14" t="str">
@@ -2824,11 +3375,16 @@
         <v>Will Pass Leakage Current Test</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.3">
       <c r="G42" s="15"/>
+    </row>
+    <row r="43" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G43" t="s">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G41">
@@ -2856,81 +3412,81 @@
   <sheetData>
     <row r="25" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C25" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" s="5">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C26" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" s="5">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C28" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D28" s="5">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C29" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D29" s="5">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C31" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="5">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C33" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D33" s="6">
         <f>230*SQRT(2)</f>
         <v>325.26911934581187</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C35" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="6">
         <f>1.1*D33</f>
         <v>357.79603128039309</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="3:6" x14ac:dyDescent="0.3">
@@ -2940,116 +3496,116 @@
     </row>
     <row r="37" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C37" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D37" s="5">
         <f>(D25*10^-6)+(D26*10^-6)+(D31*10^-9)+(1/((1/(D28*10^-9))+(1/(D29*10^-9))))</f>
-        <v>2.1028E-6</v>
+        <v>4.4750000000000004E-6</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D38" s="13">
         <f>D37*10^6</f>
-        <v>2.1028000000000002</v>
+        <v>4.4750000000000005</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C39" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D39" s="6">
         <f>1.2*D38</f>
-        <v>2.5233600000000003</v>
+        <v>5.37</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="3:6" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C47" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D47" s="6">
         <f>(((-LN(60/D35))/1)^-1)/(D39*10^-6)</f>
-        <v>221938.22314171676</v>
+        <v>104288.64706645854</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D48">
         <f>D47/1000</f>
-        <v>221.93822314171678</v>
+        <v>104.28864706645854</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C56" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" s="16">
+        <v>230</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="D56" s="17">
-        <v>230</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="58" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C58" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D58" s="17">
+        <v>74</v>
+      </c>
+      <c r="D58" s="16">
         <f>1.1*D56</f>
         <v>253.00000000000003</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C60" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D60" s="5">
-        <f>1.1*220</f>
-        <v>242.00000000000003</v>
+        <f>1.1*1*10^6</f>
+        <v>1100000</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="3:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C62" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D62" s="5">
         <f>(D58)^2/(D60*10^3)</f>
-        <v>0.26450000000000001</v>
+        <v>5.819000000000001E-5</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C63" s="10"/>
       <c r="D63" s="10">
         <f>D62*1000</f>
-        <v>264.5</v>
+        <v>5.8190000000000013E-2</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3068,87 +3624,87 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="18" t="s">
-        <v>100</v>
+      <c r="B18" s="17" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="16">
+        <v>230</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="D19" s="17">
-        <v>230</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C21" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D21" s="6">
         <f>D19*1.21</f>
         <v>278.3</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C23" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="17">
+        <v>97</v>
+      </c>
+      <c r="D23" s="16">
         <f>D21*1.078</f>
         <v>300.00740000000002</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B25" s="18" t="s">
-        <v>101</v>
+      <c r="B25" s="17" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="16">
+        <v>24</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="D26" s="17">
-        <v>24</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C28" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D28" s="6">
         <f>D26*1.21</f>
         <v>29.04</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="25.8" x14ac:dyDescent="0.3">
       <c r="C30" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" s="17">
+        <v>97</v>
+      </c>
+      <c r="D30" s="16">
         <f>D28*1.078</f>
         <v>31.305120000000002</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3170,63 +3726,63 @@
   <sheetData>
     <row r="3" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="2:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
